--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2020_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2020_antofagasta.xlsx
@@ -48,6 +48,9 @@
     <t xml:space="preserve">Sierra Gorda</t>
   </si>
   <si>
+    <t xml:space="preserve">Taltal</t>
+  </si>
+  <si>
     <t xml:space="preserve">María Elena</t>
   </si>
   <si>
@@ -57,9 +60,6 @@
     <t xml:space="preserve">Tocopilla</t>
   </si>
   <si>
-    <t xml:space="preserve">Taltal</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:14</t>
+    <t xml:space="preserve">2026-09-10 00:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -567,7 +567,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2302</v>
+        <v>2104</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -580,7 +580,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2201</v>
+        <v>2302</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -593,7 +593,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2301</v>
+        <v>2201</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -603,10 +603,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2101</v>
+        <v>2301</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -616,10 +616,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2104</v>
+        <v>2101</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>

--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2020_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2020_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:18</t>
+    <t xml:space="preserve">2026-09-18 10:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
